--- a/jira_export_2026-10-13.xlsx
+++ b/jira_export_2026-10-13.xlsx
@@ -815,7 +815,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>177 h</t>
+          <t>180 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -829,7 +829,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -933,7 +933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -949,7 +949,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2478,32 +2478,32 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35261</t>
+          <t>PDMDEP-35295</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
+          <t>[CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)] - MM - Up - LiExp - Pastell (iParapheur)</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>Reprise des données TLPE</t>
+          <t>MM - Up - LiExp - Pastell (iParapheur)</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G25" s="11" t="inlineStr">
@@ -2513,22 +2513,30 @@
       </c>
       <c r="H25" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>25/08/2026</t>
+          <t>27/08/2026</t>
         </is>
       </c>
       <c r="J25" s="11" t="n">
         <v>2</v>
       </c>
       <c r="K25" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L25" s="11" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L25" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-35301</t>
+        </is>
+      </c>
+      <c r="M25" s="11" t="inlineStr">
+        <is>
+          <t>00179371</t>
+        </is>
+      </c>
       <c r="N25" s="12" t="n">
         <v>0</v>
       </c>
@@ -2542,12 +2550,12 @@
     <row r="26">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35206</t>
+          <t>PDMDEP-35261</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>[VILLE DE VILLEURBANNE] - Reprise des données TLPE</t>
         </is>
       </c>
       <c r="C26" s="14" t="inlineStr">
@@ -2557,12 +2565,12 @@
       </c>
       <c r="D26" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E26" s="14" t="inlineStr">
         <is>
-          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
+          <t>Reprise des données TLPE</t>
         </is>
       </c>
       <c r="F26" s="14" t="inlineStr">
@@ -2577,34 +2585,26 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
         <is>
-          <t>24/08/2026</t>
+          <t>25/08/2026</t>
         </is>
       </c>
       <c r="J26" s="14" t="n">
         <v>2</v>
       </c>
       <c r="K26" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-35212</t>
-        </is>
-      </c>
-      <c r="M26" s="14" t="inlineStr">
-        <is>
-          <t>00179038</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="L26" s="14" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
       <c r="N26" s="15" t="n">
-        <v>250.5</v>
-      </c>
-      <c r="O26" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="15" t="n">
@@ -2614,12 +2614,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-35130</t>
+          <t>PDMDEP-35206</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>[VILLE DE BOULOGNE-BILLANCOURT] - Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE HARNES</t>
+          <t>VILLE DE BOULOGNE-BILLANCOURT</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
+          <t>Hébergement - Formation ODP - Accompagnement à distance</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr">
@@ -2649,12 +2649,12 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>18/08/2026</t>
+          <t>24/08/2026</t>
         </is>
       </c>
       <c r="J27" s="11" t="n">
@@ -2665,16 +2665,16 @@
       </c>
       <c r="L27" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-35139</t>
+          <t>PDMDEP-35212</t>
         </is>
       </c>
       <c r="M27" s="11" t="inlineStr">
         <is>
-          <t>00178821</t>
+          <t>00179038</t>
         </is>
       </c>
       <c r="N27" s="12" t="n">
-        <v>1465.2</v>
+        <v>250.5</v>
       </c>
       <c r="O27" s="16" t="n">
         <v>0</v>
@@ -2686,12 +2686,12 @@
     <row r="28">
       <c r="A28" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-35105</t>
+          <t>PDMDEP-35130</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
+          <t>[COMMUNE DE HARNES] - Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="C28" s="14" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="D28" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CARNAC</t>
+          <t>COMMUNE DE HARNES</t>
         </is>
       </c>
       <c r="E28" s="14" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Migration de GEODP-Placier + remise en service CB (jamais installé ils payent deja un abo)</t>
         </is>
       </c>
       <c r="F28" s="14" t="inlineStr">
@@ -2737,16 +2737,16 @@
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-35114</t>
+          <t>PDMDEP-35139</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
         <is>
-          <t>00178806</t>
+          <t>00178821</t>
         </is>
       </c>
       <c r="N28" s="15" t="n">
-        <v>394</v>
+        <v>1465.2</v>
       </c>
       <c r="O28" s="16" t="n">
         <v>0</v>
@@ -2758,32 +2758,32 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34975</t>
+          <t>PDMDEP-35105</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>[MAIRIE DE CARNAC] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE SURESNES</t>
+          <t>MAIRIE DE CARNAC</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G29" s="11" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>06/08/2026</t>
+          <t>18/08/2026</t>
         </is>
       </c>
       <c r="J29" s="11" t="n">
@@ -2809,16 +2809,16 @@
       </c>
       <c r="L29" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34979</t>
+          <t>PDMDEP-35114</t>
         </is>
       </c>
       <c r="M29" s="11" t="inlineStr">
         <is>
-          <t>00178226</t>
+          <t>00178806</t>
         </is>
       </c>
       <c r="N29" s="12" t="n">
-        <v>1100</v>
+        <v>394</v>
       </c>
       <c r="O29" s="16" t="n">
         <v>0</v>
@@ -2830,32 +2830,32 @@
     <row r="30">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34953</t>
+          <t>PDMDEP-34975</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE BAIE-MAHAULT] - Acquisition GEODP Caisse </t>
+          <t>[VILLE DE SURESNES] - Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BAIE-MAHAULT</t>
+          <t>VILLE DE SURESNES</t>
         </is>
       </c>
       <c r="E30" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Achat module Caisse </t>
+          <t>Migration Littéralis vers nouveau serveur+ montée de version Test et Prod</t>
         </is>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>05/08/2026</t>
+          <t>06/08/2026</t>
         </is>
       </c>
       <c r="J30" s="14" t="n">
@@ -2881,16 +2881,16 @@
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34961</t>
+          <t>PDMDEP-34979</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
         <is>
-          <t>00178176</t>
+          <t>00178226</t>
         </is>
       </c>
       <c r="N30" s="15" t="n">
-        <v>810</v>
+        <v>1100</v>
       </c>
       <c r="O30" s="16" t="n">
         <v>0</v>
@@ -2902,32 +2902,32 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34925</t>
+          <t>PDMDEP-34953</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
+          <t xml:space="preserve">[COMMUNE DE BAIE-MAHAULT] - Acquisition GEODP Caisse </t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
+          <t>COMMUNE DE BAIE-MAHAULT</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>AME multi-communes acheté par la CC</t>
+          <t xml:space="preserve">Achat module Caisse </t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G31" s="11" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>04/08/2026</t>
+          <t>05/08/2026</t>
         </is>
       </c>
       <c r="J31" s="11" t="n">
@@ -2953,16 +2953,16 @@
       </c>
       <c r="L31" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34929</t>
+          <t>PDMDEP-34961</t>
         </is>
       </c>
       <c r="M31" s="11" t="inlineStr">
         <is>
-          <t>00178034</t>
+          <t>00178176</t>
         </is>
       </c>
       <c r="N31" s="12" t="n">
-        <v>960</v>
+        <v>810</v>
       </c>
       <c r="O31" s="16" t="n">
         <v>0</v>
@@ -2974,32 +2974,32 @@
     <row r="32">
       <c r="A32" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34925</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
+          <t>[COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE] - AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNAUTE DE COMMUNES DU SUD ESTUAIRE</t>
         </is>
       </c>
       <c r="E32" s="14" t="inlineStr">
         <is>
-          <t>GEODP PLACIER</t>
+          <t>AME multi-communes acheté par la CC</t>
         </is>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -3009,32 +3009,32 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>04/08/2026</t>
         </is>
       </c>
       <c r="J32" s="14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K32" s="14" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34929</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00178034</t>
         </is>
       </c>
       <c r="N32" s="15" t="n">
-        <v>1073.25</v>
+        <v>960</v>
       </c>
       <c r="O32" s="16" t="n">
         <v>0</v>
@@ -3046,32 +3046,32 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
+          <t>[MAIRIE DE SAINT-ISMIER] - Acquisition GEODP Placier</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>Crédits d'heure (14h)</t>
+          <t>GEODP PLACIER</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G33" s="11" t="inlineStr">
@@ -3081,12 +3081,12 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J33" s="11" t="n">
@@ -3097,16 +3097,16 @@
       </c>
       <c r="L33" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="M33" s="11" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="N33" s="12" t="n">
-        <v>243.6</v>
+        <v>1073.25</v>
       </c>
       <c r="O33" s="16" t="n">
         <v>0</v>
@@ -3118,32 +3118,32 @@
     <row r="34">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34694</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
+          <t>[VILLE DE VILLEURBANNE] - Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
         <is>
-          <t>Commune du Tampon</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E34" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t>Crédits d'heure (14h)</t>
         </is>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
         <is>
-          <t>22/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="J34" s="14" t="n">
@@ -3169,16 +3169,16 @@
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34701</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
         <is>
-          <t>00176675</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="N34" s="15" t="n">
-        <v>2763.25</v>
+        <v>243.6</v>
       </c>
       <c r="O34" s="16" t="n">
         <v>0</v>
@@ -3190,12 +3190,12 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34676</t>
+          <t>PDMDEP-34694</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
+          <t>[COMMUNE DU TAMPON] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>Commune des Ponts de Ce</t>
+          <t>Commune du Tampon</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
@@ -3237,37 +3237,37 @@
         <v>3</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34683</t>
+          <t>PDMDEP-34701</t>
         </is>
       </c>
       <c r="M35" s="11" t="inlineStr">
         <is>
-          <t>00176614</t>
+          <t>00176675</t>
         </is>
       </c>
       <c r="N35" s="12" t="n">
-        <v>215</v>
-      </c>
-      <c r="O35" s="12" t="n">
-        <v>516</v>
+        <v>2763.25</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P35" s="12" t="n">
-        <v>129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34659</t>
+          <t>PDMDEP-34676</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C36" s="14" t="inlineStr">
@@ -3282,7 +3282,7 @@
       </c>
       <c r="E36" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F36" s="14" t="inlineStr">
@@ -3309,11 +3309,11 @@
         <v>3</v>
       </c>
       <c r="K36" s="14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34666</t>
+          <t>PDMDEP-34683</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -3322,44 +3322,44 @@
         </is>
       </c>
       <c r="N36" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="O36" s="16" t="n">
-        <v>0</v>
+        <v>215</v>
+      </c>
+      <c r="O36" s="15" t="n">
+        <v>516</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>0</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34650</t>
+          <t>PDMDEP-34659</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>[CD 01] -  Transfert de compétence Montée de version</t>
+          <t>[COMMUNE DES PONTS DE CE] - Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+          <t>Commune des Ponts de Ce</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
+          <t>Migration GEODP TLPE</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G37" s="11" t="inlineStr">
@@ -3369,34 +3369,34 @@
       </c>
       <c r="H37" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I37" s="11" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>22/07/2026</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K37" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L37" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34654</t>
+          <t>PDMDEP-34666</t>
         </is>
       </c>
       <c r="M37" s="11" t="inlineStr">
         <is>
-          <t>00176582</t>
+          <t>00176614</t>
         </is>
       </c>
       <c r="N37" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="O37" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P37" s="12" t="n">
@@ -3406,32 +3406,32 @@
     <row r="38">
       <c r="A38" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34631</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
+          <t>[CD 01] -  Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E38" s="14" t="inlineStr">
         <is>
-          <t>acquisition geodp caisse</t>
+          <t xml:space="preserve"> Transfert de compétence Montée de version</t>
         </is>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
@@ -3453,22 +3453,22 @@
         <v>3</v>
       </c>
       <c r="K38" s="14" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34640</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
         <is>
-          <t>00176477</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="N38" s="15" t="n">
-        <v>1620</v>
-      </c>
-      <c r="O38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P38" s="15" t="n">
@@ -3478,12 +3478,12 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34580</t>
+          <t>PDMDEP-34631</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
+          <t>[COMMUNE DE SAINT-HILAIRE-DE-RIEZ] - Acquisition GEODP Caisse</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE RIEZ</t>
+          <t>COMMUNE DE SAINT-HILAIRE-DE-RIEZ</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER simple</t>
+          <t>acquisition geodp caisse</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr">
@@ -3513,32 +3513,32 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I39" s="11" t="inlineStr">
         <is>
-          <t>16/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="K39" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L39" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34589</t>
+          <t>PDMDEP-34640</t>
         </is>
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>00176128</t>
+          <t>00176477</t>
         </is>
       </c>
       <c r="N39" s="12" t="n">
-        <v>936</v>
+        <v>1620</v>
       </c>
       <c r="O39" s="16" t="n">
         <v>0</v>
@@ -3550,32 +3550,32 @@
     <row r="40">
       <c r="A40" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34580</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
+          <t>[COMMUNE DE RIEZ] - Migration GEODP Placier Simple</t>
         </is>
       </c>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE RIEZ</t>
         </is>
       </c>
       <c r="E40" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
+          <t>MIGRATION GEODP PLACIER simple</t>
         </is>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>16/07/2026</t>
         </is>
       </c>
       <c r="J40" s="14" t="n">
@@ -3601,16 +3601,16 @@
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34589</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00176128</t>
         </is>
       </c>
       <c r="N40" s="15" t="n">
-        <v>344</v>
+        <v>936</v>
       </c>
       <c r="O40" s="16" t="n">
         <v>0</v>
@@ -3622,32 +3622,32 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34319</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE CLICHY] - PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>Commune de Mouscron (BE)</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier</t>
+          <t xml:space="preserve">PRESTATION DE MODELISATION + integration RODP </t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
@@ -3657,32 +3657,32 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I41" s="11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="J41" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L41" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34326</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>00171691</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="N41" s="12" t="n">
-        <v>153.9</v>
+        <v>344</v>
       </c>
       <c r="O41" s="16" t="n">
         <v>0</v>
@@ -3694,27 +3694,27 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34303</t>
+          <t>PDMDEP-34319</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
+          <t>[Commune de Mouscron (BE)] - Migration GEODP Placier</t>
         </is>
       </c>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE GAP</t>
+          <t>Commune de Mouscron (BE)</t>
         </is>
       </c>
       <c r="E42" s="14" t="inlineStr">
         <is>
-          <t>Migration Placier + ODP</t>
+          <t>Migration GEODP Placier</t>
         </is>
       </c>
       <c r="F42" s="14" t="inlineStr">
@@ -3745,16 +3745,16 @@
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34310</t>
+          <t>PDMDEP-34326</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
         <is>
-          <t>00171605</t>
+          <t>00171691</t>
         </is>
       </c>
       <c r="N42" s="15" t="n">
-        <v>4150</v>
+        <v>153.9</v>
       </c>
       <c r="O42" s="16" t="n">
         <v>0</v>
@@ -3766,27 +3766,27 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-34303</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[COMMUNE DE GAP] - Migration Placier + ODP</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE GAP</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t>Migration Placier + ODP</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
@@ -3806,21 +3806,29 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K43" s="11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L43" s="11" t="inlineStr"/>
-      <c r="M43" s="11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L43" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34310</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>00171605</t>
+        </is>
+      </c>
       <c r="N43" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="12" t="n">
+        <v>4150</v>
+      </c>
+      <c r="O43" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P43" s="12" t="n">
@@ -3830,27 +3838,27 @@
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="E44" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="F44" s="14" t="inlineStr">
@@ -3860,7 +3868,7 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
@@ -3877,22 +3885,14 @@
         <v>4</v>
       </c>
       <c r="K44" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-34258</t>
-        </is>
-      </c>
-      <c r="M44" s="14" t="inlineStr">
-        <is>
-          <t>00171361</t>
-        </is>
-      </c>
+        <v>3.5</v>
+      </c>
+      <c r="L44" s="14" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
       <c r="N44" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="O44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P44" s="15" t="n">
@@ -3902,32 +3902,32 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34229</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>GRC + Connecteur</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
@@ -3937,69 +3937,69 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="L45" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34235</t>
+          <t>PDMDEP-34258</t>
         </is>
       </c>
       <c r="M45" s="11" t="inlineStr">
         <is>
-          <t>00171333</t>
+          <t>00171361</t>
         </is>
       </c>
       <c r="N45" s="12" t="n">
-        <v>2649.6</v>
+        <v>2500</v>
       </c>
       <c r="O45" s="16" t="n">
-        <v>576</v>
+        <v>0</v>
       </c>
       <c r="P45" s="12" t="n">
-        <v>67.76000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34208</t>
+          <t>PDMDEP-34229</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
+          <t>[DIJON METROPOLE] - GRC + Connecteur</t>
         </is>
       </c>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHATEAUGIRON</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E46" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2</t>
+          <t>GRC + Connecteur</t>
         </is>
       </c>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -4009,49 +4009,49 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="J46" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K46" s="14" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34216</t>
+          <t>PDMDEP-34235</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>00171155</t>
+          <t>00171333</t>
         </is>
       </c>
       <c r="N46" s="15" t="n">
-        <v>175</v>
+        <v>2649.6</v>
       </c>
       <c r="O46" s="16" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="P46" s="15" t="n">
-        <v>0</v>
+        <v>67.76000000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34192</t>
+          <t>PDMDEP-34208</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Macon ] - GEODP Placier</t>
+          <t>[COMMUNE DE CHATEAUGIRON] - Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
@@ -4061,12 +4061,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commune de Macon </t>
+          <t>COMMUNE DE CHATEAUGIRON</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>GEODP Placier</t>
+          <t>Migration GEODP Placier 2</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="H47" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
@@ -4093,20 +4093,20 @@
         <v>4</v>
       </c>
       <c r="K47" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34201</t>
+          <t>PDMDEP-34216</t>
         </is>
       </c>
       <c r="M47" s="11" t="inlineStr">
         <is>
-          <t>00171162</t>
+          <t>00171155</t>
         </is>
       </c>
       <c r="N47" s="12" t="n">
-        <v>775.6</v>
+        <v>175</v>
       </c>
       <c r="O47" s="16" t="n">
         <v>0</v>
@@ -4118,27 +4118,27 @@
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34169</t>
+          <t>PDMDEP-34192</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[Commune de Macon ] - GEODP Placier</t>
         </is>
       </c>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
+          <t xml:space="preserve">Commune de Macon </t>
         </is>
       </c>
       <c r="E48" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>GEODP Placier</t>
         </is>
       </c>
       <c r="F48" s="14" t="inlineStr">
@@ -4153,32 +4153,32 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="J48" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K48" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34227</t>
+          <t>PDMDEP-34201</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>2026-0210095</t>
+          <t>00171162</t>
         </is>
       </c>
       <c r="N48" s="15" t="n">
-        <v>5388.936</v>
+        <v>775.6</v>
       </c>
       <c r="O48" s="16" t="n">
         <v>0</v>
@@ -4190,27 +4190,27 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34081</t>
+          <t>PDMDEP-34169</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
+          <t>[COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ERQUY</t>
+          <t>COMMUNAUTE URBAINE ANGERS LOIRE METROPOLE</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 2 + Pax</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="J49" s="11" t="n">
@@ -4241,16 +4241,16 @@
       </c>
       <c r="L49" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34090</t>
+          <t>PDMDEP-34227</t>
         </is>
       </c>
       <c r="M49" s="11" t="inlineStr">
         <is>
-          <t>00170724</t>
+          <t>2026-0210095</t>
         </is>
       </c>
       <c r="N49" s="12" t="n">
-        <v>177.5</v>
+        <v>5388.936</v>
       </c>
       <c r="O49" s="16" t="n">
         <v>0</v>
@@ -4262,27 +4262,27 @@
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34064</t>
+          <t>PDMDEP-34081</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
+          <t>[COMMUNE DE ERQUY] - Migration GEODP Placier + Pax</t>
         </is>
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VANNES</t>
+          <t>COMMUNE DE ERQUY</t>
         </is>
       </c>
       <c r="E50" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
+          <t>Migration GEODP 2 + Pax</t>
         </is>
       </c>
       <c r="F50" s="14" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H50" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="J50" s="14" t="n">
@@ -4313,16 +4313,16 @@
       </c>
       <c r="L50" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34070</t>
+          <t>PDMDEP-34090</t>
         </is>
       </c>
       <c r="M50" s="14" t="inlineStr">
         <is>
-          <t>00170468</t>
+          <t>00170724</t>
         </is>
       </c>
       <c r="N50" s="15" t="n">
-        <v>1700</v>
+        <v>177.5</v>
       </c>
       <c r="O50" s="16" t="n">
         <v>0</v>
@@ -4334,27 +4334,27 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34064</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[VILLE DE VANNES] - ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VANNES</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">ORMC pour GEODP PLACIER </t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr">
@@ -4369,64 +4369,64 @@
       </c>
       <c r="H51" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="J51" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K51" s="11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34021</t>
+          <t>PDMDEP-34070</t>
         </is>
       </c>
       <c r="M51" s="11" t="inlineStr">
         <is>
-          <t>00170494</t>
+          <t>00170468</t>
         </is>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1786.1</v>
+        <v>1700</v>
       </c>
       <c r="O51" s="16" t="n">
-        <v>909.9</v>
+        <v>0</v>
       </c>
       <c r="P51" s="12" t="n">
-        <v>303.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33985</t>
+          <t>PDMDEP-34012</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
         </is>
       </c>
       <c r="C52" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE QUIMPERLE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E52" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
+          <t>Migration module Placier</t>
         </is>
       </c>
       <c r="F52" s="14" t="inlineStr">
@@ -4446,64 +4446,64 @@
       </c>
       <c r="I52" s="14" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="J52" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K52" s="14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33991</t>
+          <t>PDMDEP-34021</t>
         </is>
       </c>
       <c r="M52" s="14" t="inlineStr">
         <is>
-          <t>00170408</t>
+          <t>00170494</t>
         </is>
       </c>
       <c r="N52" s="15" t="n">
-        <v>170</v>
+        <v>1786.1</v>
       </c>
       <c r="O52" s="16" t="n">
-        <v>0</v>
+        <v>909.9</v>
       </c>
       <c r="P52" s="15" t="n">
-        <v>0</v>
+        <v>303.3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33949</t>
+          <t>PDMDEP-33985</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
+          <t>[COMMUNE DE QUIMPERLE] - Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>Commune de Colmar</t>
+          <t>COMMUNE DE QUIMPERLE</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Littéralis Expert</t>
+          <t>Migration GEODP 1 vers GEODP 2 (Placier)</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="H53" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="J53" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K53" s="11" t="n">
-        <v>10.75</v>
+        <v>0</v>
       </c>
       <c r="L53" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33955</t>
+          <t>PDMDEP-33991</t>
         </is>
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>00170302</t>
+          <t>00170408</t>
         </is>
       </c>
       <c r="N53" s="12" t="n">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="O53" s="16" t="n">
         <v>0</v>
@@ -4550,27 +4550,27 @@
     <row r="54">
       <c r="A54" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33940</t>
+          <t>PDMDEP-33949</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Thionville] - AME </t>
+          <t>[Commune de Colmar] - Modélisation Littéralis Expert et Démarrage Prod</t>
         </is>
       </c>
       <c r="C54" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
         <is>
-          <t>Commune de Thionville</t>
+          <t>Commune de Colmar</t>
         </is>
       </c>
       <c r="E54" s="14" t="inlineStr">
         <is>
-          <t>AME Littéralis Expert</t>
+          <t>Modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="F54" s="14" t="inlineStr">
@@ -4597,57 +4597,57 @@
         <v>4</v>
       </c>
       <c r="K54" s="14" t="n">
-        <v>2.25</v>
+        <v>10.75</v>
       </c>
       <c r="L54" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33944</t>
+          <t>PDMDEP-33955</t>
         </is>
       </c>
       <c r="M54" s="14" t="inlineStr">
         <is>
-          <t>00170299</t>
+          <t>00170302</t>
         </is>
       </c>
       <c r="N54" s="15" t="n">
-        <v>484</v>
+        <v>3000</v>
       </c>
       <c r="O54" s="16" t="n">
-        <v>308</v>
+        <v>0</v>
       </c>
       <c r="P54" s="15" t="n">
-        <v>136.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33906</t>
+          <t>PDMDEP-33940</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
+          <t xml:space="preserve">[Commune de Thionville] - AME </t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>Commune d'Arras</t>
+          <t>Commune de Thionville</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP ODP (Terrasse)</t>
+          <t>AME Littéralis Expert</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4657,64 +4657,64 @@
       </c>
       <c r="H55" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="J55" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K55" s="11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L55" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33914</t>
+          <t>PDMDEP-33944</t>
         </is>
       </c>
       <c r="M55" s="11" t="inlineStr">
         <is>
-          <t>00167633</t>
+          <t>00170299</t>
         </is>
       </c>
       <c r="N55" s="12" t="n">
-        <v>700</v>
+        <v>484</v>
       </c>
       <c r="O55" s="16" t="n">
-        <v>0</v>
+        <v>308</v>
       </c>
       <c r="P55" s="12" t="n">
-        <v>0</v>
+        <v>136.89</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33841</t>
+          <t>PDMDEP-33906</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>[Commune d'Arras] - Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="C56" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
         <is>
-          <t>Commune de Nans les Pins</t>
+          <t>Commune d'Arras</t>
         </is>
       </c>
       <c r="E56" s="14" t="inlineStr">
         <is>
-          <t>MIGRATION GEODP PLACIER SIMPLE</t>
+          <t>Migration GEODP ODP (Terrasse)</t>
         </is>
       </c>
       <c r="F56" s="14" t="inlineStr">
@@ -4745,16 +4745,16 @@
       </c>
       <c r="L56" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33850</t>
+          <t>PDMDEP-33914</t>
         </is>
       </c>
       <c r="M56" s="14" t="inlineStr">
         <is>
-          <t>00161103</t>
+          <t>00167633</t>
         </is>
       </c>
       <c r="N56" s="15" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="O56" s="16" t="n">
         <v>0</v>
@@ -4766,32 +4766,32 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33813</t>
+          <t>PDMDEP-33841</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
+          <t>[Commune de Nans les Pins] - MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de Nans les Pins</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>Modélisation Seyne S/ Mer</t>
+          <t>MIGRATION GEODP PLACIER SIMPLE</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
@@ -4801,32 +4801,32 @@
       </c>
       <c r="H57" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="J57" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K57" s="11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L57" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33817</t>
+          <t>PDMDEP-33850</t>
         </is>
       </c>
       <c r="M57" s="11" t="inlineStr">
         <is>
-          <t>00169865</t>
+          <t>00161103</t>
         </is>
       </c>
       <c r="N57" s="12" t="n">
-        <v>186.235</v>
+        <v>170</v>
       </c>
       <c r="O57" s="16" t="n">
         <v>0</v>
@@ -4838,12 +4838,12 @@
     <row r="58">
       <c r="A58" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33813</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="C58" s="14" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E58" s="14" t="inlineStr">
         <is>
-          <t>Purge arrêtés temporaires</t>
+          <t>Modélisation Seyne S/ Mer</t>
         </is>
       </c>
       <c r="F58" s="14" t="inlineStr">
@@ -4885,20 +4885,20 @@
         <v>4</v>
       </c>
       <c r="K58" s="14" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="L58" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33808</t>
+          <t>PDMDEP-33817</t>
         </is>
       </c>
       <c r="M58" s="14" t="inlineStr">
         <is>
-          <t>00169856</t>
+          <t>00169865</t>
         </is>
       </c>
       <c r="N58" s="15" t="n">
-        <v>1890</v>
+        <v>186.235</v>
       </c>
       <c r="O58" s="16" t="n">
         <v>0</v>
@@ -4910,27 +4910,27 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33790</t>
+          <t>PDMDEP-33804</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Commande modélisation supplémentaire </t>
+          <t>Purge arrêtés temporaires</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr">
@@ -4950,27 +4950,27 @@
       </c>
       <c r="I59" s="11" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="J59" s="11" t="n">
         <v>4</v>
       </c>
       <c r="K59" s="11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L59" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33794</t>
+          <t>PDMDEP-33808</t>
         </is>
       </c>
       <c r="M59" s="11" t="inlineStr">
         <is>
-          <t>00169697</t>
+          <t>00169856</t>
         </is>
       </c>
       <c r="N59" s="12" t="n">
-        <v>400</v>
+        <v>1890</v>
       </c>
       <c r="O59" s="16" t="n">
         <v>0</v>
@@ -4982,12 +4982,12 @@
     <row r="60">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33739</t>
+          <t>PDMDEP-33790</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
+          <t>[CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91)] - Commande modélisation supplémentaire - 6,5j</t>
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
         </is>
       </c>
       <c r="E60" s="14" t="inlineStr">
         <is>
-          <t>UPSELL PASTELL + DA DPA</t>
+          <t xml:space="preserve">Commande modélisation supplémentaire </t>
         </is>
       </c>
       <c r="F60" s="14" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="J60" s="14" t="n">
@@ -5033,16 +5033,16 @@
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33745</t>
+          <t>PDMDEP-33794</t>
         </is>
       </c>
       <c r="M60" s="14" t="inlineStr">
         <is>
-          <t>00169509</t>
+          <t>00169697</t>
         </is>
       </c>
       <c r="N60" s="15" t="n">
-        <v>552</v>
+        <v>400</v>
       </c>
       <c r="O60" s="16" t="n">
         <v>0</v>
@@ -5054,27 +5054,27 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33729</t>
+          <t>PDMDEP-33739</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>[COMMUNE DU POIRE SUR VIE (MAIRIE)] - UPSELL Pastell + Portail DA DPA</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
+          <t>COMMUNE DU POIRE SUR VIE (MAIRIE)</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
+          <t>UPSELL PASTELL + DA DPA</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr">
@@ -5101,22 +5101,22 @@
         <v>4</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>0.25</v>
+        <v>3.5</v>
       </c>
       <c r="L61" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33733</t>
+          <t>PDMDEP-33745</t>
         </is>
       </c>
       <c r="M61" s="11" t="inlineStr">
         <is>
-          <t>00169480</t>
+          <t>00169509</t>
         </is>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="12" t="n">
+        <v>552</v>
+      </c>
+      <c r="O61" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P61" s="12" t="n">
@@ -5126,32 +5126,32 @@
     <row r="62">
       <c r="A62" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33597</t>
+          <t>PDMDEP-33729</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">[VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information] - MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="C62" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>Commune de Trets</t>
+          <t>VILLE DE NEUILLY SUR SEINE - Direction des systèmes d'information</t>
         </is>
       </c>
       <c r="E62" s="14" t="inlineStr">
         <is>
-          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
+          <t xml:space="preserve">MONTEE DE VERSION LITT EXP  test et prod </t>
         </is>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -5166,29 +5166,29 @@
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="J62" s="14" t="n">
         <v>4</v>
       </c>
       <c r="K62" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L62" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33605</t>
+          <t>PDMDEP-33733</t>
         </is>
       </c>
       <c r="M62" s="14" t="inlineStr">
         <is>
-          <t>00168993</t>
+          <t>00169480</t>
         </is>
       </c>
       <c r="N62" s="15" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P62" s="15" t="n">
@@ -5198,27 +5198,27 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33517</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE MONTREUIL</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr">
@@ -5233,32 +5233,32 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I63" s="11" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J63" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K63" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L63" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33526</t>
+          <t>PDMDEP-33605</t>
         </is>
       </c>
       <c r="M63" s="11" t="inlineStr">
         <is>
-          <t>00168179</t>
+          <t>00168993</t>
         </is>
       </c>
       <c r="N63" s="12" t="n">
-        <v>2000</v>
+        <v>203.5</v>
       </c>
       <c r="O63" s="16" t="n">
         <v>0</v>
@@ -5270,27 +5270,27 @@
     <row r="64">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33500</t>
+          <t>PDMDEP-33517</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
+          <t>[VILLE DE MONTREUIL] - MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mairie de Carcès </t>
+          <t>VILLE DE MONTREUIL</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
+          <t>MM - Cross - GeODP Terrasse - Acquisition</t>
         </is>
       </c>
       <c r="F64" s="14" t="inlineStr">
@@ -5321,16 +5321,16 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33509</t>
+          <t>PDMDEP-33526</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>00168117</t>
+          <t>00168179</t>
         </is>
       </c>
       <c r="N64" s="15" t="n">
-        <v>203.5</v>
+        <v>2000</v>
       </c>
       <c r="O64" s="16" t="n">
         <v>0</v>
@@ -5342,32 +5342,32 @@
     <row r="65">
       <c r="A65" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33471</t>
+          <t>PDMDEP-33500</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
+          <t xml:space="preserve">[Mairie de Carcès ] - GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D AUCH</t>
+          <t xml:space="preserve">Mairie de Carcès </t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>FDS Facture LiS</t>
+          <t xml:space="preserve">GEODP PLACIER avec PAIEMENT CB </t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G65" s="11" t="inlineStr">
@@ -5377,12 +5377,12 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I65" s="11" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="J65" s="11" t="n">
@@ -5393,16 +5393,16 @@
       </c>
       <c r="L65" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33475</t>
+          <t>PDMDEP-33509</t>
         </is>
       </c>
       <c r="M65" s="11" t="inlineStr">
         <is>
-          <t>00168025</t>
+          <t>00168117</t>
         </is>
       </c>
       <c r="N65" s="12" t="n">
-        <v>171.4</v>
+        <v>203.5</v>
       </c>
       <c r="O65" s="16" t="n">
         <v>0</v>
@@ -5414,27 +5414,27 @@
     <row r="66">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33451</t>
+          <t>PDMDEP-33471</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
+          <t>[COMMUNE D AUCH] - FDS Facture LiS</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHATELLERAULT</t>
+          <t>COMMUNE D AUCH</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
         <is>
-          <t>FDS pour Littéralis Expert</t>
+          <t>FDS Facture LiS</t>
         </is>
       </c>
       <c r="F66" s="14" t="inlineStr">
@@ -5465,16 +5465,16 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33455</t>
+          <t>PDMDEP-33475</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
         <is>
-          <t>00167958</t>
+          <t>00168025</t>
         </is>
       </c>
       <c r="N66" s="15" t="n">
-        <v>400</v>
+        <v>171.4</v>
       </c>
       <c r="O66" s="16" t="n">
         <v>0</v>
@@ -5486,32 +5486,32 @@
     <row r="67">
       <c r="A67" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33431</t>
+          <t>PDMDEP-33451</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
+          <t>[VILLE DE CHATELLERAULT] - FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
+          <t>VILLE DE CHATELLERAULT</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
+          <t>FDS pour Littéralis Expert</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G67" s="11" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J67" s="11" t="n">
@@ -5537,16 +5537,16 @@
       </c>
       <c r="L67" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33440</t>
+          <t>PDMDEP-33455</t>
         </is>
       </c>
       <c r="M67" s="11" t="inlineStr">
         <is>
-          <t>00166923</t>
+          <t>00167958</t>
         </is>
       </c>
       <c r="N67" s="12" t="n">
-        <v>6177.52</v>
+        <v>400</v>
       </c>
       <c r="O67" s="16" t="n">
         <v>0</v>
@@ -5558,27 +5558,27 @@
     <row r="68">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33395</t>
+          <t>PDMDEP-33431</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">[COMMUNE DE VERSAILLES] - Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="C68" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBELIARD</t>
+          <t xml:space="preserve">COMMUNE DE VERSAILLES </t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
+          <t xml:space="preserve">Migration multi-modules (hors taxi) </t>
         </is>
       </c>
       <c r="F68" s="14" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="H68" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="J68" s="14" t="n">
@@ -5609,16 +5609,16 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33401</t>
+          <t>PDMDEP-33440</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>00167624</t>
+          <t>00166923</t>
         </is>
       </c>
       <c r="N68" s="15" t="n">
-        <v>500</v>
+        <v>6177.52</v>
       </c>
       <c r="O68" s="16" t="n">
         <v>0</v>
@@ -5630,32 +5630,32 @@
     <row r="69">
       <c r="A69" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33311</t>
+          <t>PDMDEP-33395</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
+          <t xml:space="preserve">[COMMUNE DE MONTBELIARD] - Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>AMIENS METROPOLE</t>
+          <t>COMMUNE DE MONTBELIARD</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
+          <t xml:space="preserve">Mise en place paiement CB sur PAX présent sur la commune </t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G69" s="11" t="inlineStr">
@@ -5670,29 +5670,29 @@
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="J69" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K69" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L69" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33315</t>
+          <t>PDMDEP-33401</t>
         </is>
       </c>
       <c r="M69" s="11" t="inlineStr">
         <is>
-          <t>00167138</t>
+          <t>00167624</t>
         </is>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="12" t="n">
+        <v>500</v>
+      </c>
+      <c r="O69" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P69" s="12" t="n">
@@ -5702,12 +5702,12 @@
     <row r="70">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33304</t>
+          <t>PDMDEP-33311</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
+          <t>[AMIENS METROPOLE] -  Développement tableau facture terrasses</t>
         </is>
       </c>
       <c r="C70" s="14" t="inlineStr">
@@ -5717,12 +5717,12 @@
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>AMIENS METROPOLE</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
         <is>
-          <t>Màj carto</t>
+          <t xml:space="preserve"> MM - Up - LiExp - Dev tableau facture terrasses</t>
         </is>
       </c>
       <c r="F70" s="14" t="inlineStr">
@@ -5732,7 +5732,7 @@
       </c>
       <c r="G70" s="14" t="inlineStr">
         <is>
-          <t>Maintenance</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H70" s="14" t="inlineStr">
@@ -5742,17 +5742,25 @@
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J70" s="14" t="n">
         <v>5</v>
       </c>
       <c r="K70" s="14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="L70" s="14" t="inlineStr"/>
-      <c r="M70" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L70" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-33315</t>
+        </is>
+      </c>
+      <c r="M70" s="14" t="inlineStr">
+        <is>
+          <t>00167138</t>
+        </is>
+      </c>
       <c r="N70" s="15" t="n">
         <v>0</v>
       </c>
@@ -5766,37 +5774,37 @@
     <row r="71">
       <c r="A71" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33266</t>
+          <t>PDMDEP-33304</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>[VILLE DE VILLEURBANNE] - Màj carto</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE CAPBRETON</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
+          <t>Màj carto</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G71" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Maintenance</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -5806,29 +5814,21 @@
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="J71" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-33272</t>
-        </is>
-      </c>
-      <c r="M71" s="11" t="inlineStr">
-        <is>
-          <t>00166910</t>
-        </is>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr"/>
       <c r="N71" s="12" t="n">
-        <v>240</v>
-      </c>
-      <c r="O71" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P71" s="12" t="n">
@@ -5838,27 +5838,27 @@
     <row r="72">
       <c r="A72" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-33266</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
+          <t>[MAIRIE DE CAPBRETON] - Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>MAIRIE DE CAPBRETON</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>Migracier activité Placier vers Geodp V2</t>
+          <t>Commune dispose de Geodp Terrasses, nouveau module pour leurs marchés</t>
         </is>
       </c>
       <c r="F72" s="14" t="inlineStr">
@@ -5873,12 +5873,12 @@
       </c>
       <c r="H72" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="J72" s="14" t="n">
@@ -5889,16 +5889,16 @@
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33245</t>
+          <t>PDMDEP-33272</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>00166748</t>
+          <t>00166910</t>
         </is>
       </c>
       <c r="N72" s="15" t="n">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="O72" s="16" t="n">
         <v>0</v>
@@ -5910,32 +5910,32 @@
     <row r="73">
       <c r="A73" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33227</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>METROPOLE EUROPEENNE DE LILLE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>21 crédits d'heure</t>
+          <t>Migracier activité Placier vers Geodp V2</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G73" s="11" t="inlineStr">
@@ -5945,32 +5945,32 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="J73" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33232</t>
+          <t>PDMDEP-33245</t>
         </is>
       </c>
       <c r="M73" s="11" t="inlineStr">
         <is>
-          <t>00166708</t>
+          <t>00166748</t>
         </is>
       </c>
       <c r="N73" s="12" t="n">
-        <v>337.5</v>
+        <v>149</v>
       </c>
       <c r="O73" s="16" t="n">
         <v>0</v>
@@ -6033,16 +6033,16 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-33231</t>
+          <t>PDMDEP-33232</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>00166707</t>
+          <t>00166708</t>
         </is>
       </c>
       <c r="N74" s="15" t="n">
-        <v>320</v>
+        <v>337.5</v>
       </c>
       <c r="O74" s="16" t="n">
         <v>0</v>
@@ -6054,32 +6054,32 @@
     <row r="75">
       <c r="A75" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-33149</t>
+          <t>PDMDEP-33227</t>
         </is>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
+          <t>[METROPOLE EUROPEENNE DE LILLE] - MEL Crédits 21 heures (3j)     mai 2026</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
+          <t>METROPOLE EUROPEENNE DE LILLE</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP</t>
+          <t>21 crédits d'heure</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G75" s="11" t="inlineStr">
@@ -6089,32 +6089,32 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="J75" s="11" t="n">
         <v>5</v>
       </c>
       <c r="K75" s="11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-33158</t>
+          <t>PDMDEP-33231</t>
         </is>
       </c>
       <c r="M75" s="11" t="inlineStr">
         <is>
-          <t>00165719</t>
+          <t>00166707</t>
         </is>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1047</v>
+        <v>320</v>
       </c>
       <c r="O75" s="16" t="n">
         <v>0</v>
@@ -6126,32 +6126,32 @@
     <row r="76">
       <c r="A76" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32984</t>
+          <t>PDMDEP-33149</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
+          <t>[COMMUNE DE SIX FOURS LES PLAGES] - Migration GeODP</t>
         </is>
       </c>
       <c r="C76" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE SIX FOURS LES PLAGES</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
         <is>
-          <t>Interface Civil net finance avec Littéralis</t>
+          <t>Migration GeODP</t>
         </is>
       </c>
       <c r="F76" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="H76" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K76" s="14" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32990</t>
+          <t>PDMDEP-33158</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>00165270</t>
+          <t>00165719</t>
         </is>
       </c>
       <c r="N76" s="15" t="n">
-        <v>400</v>
+        <v>1047</v>
       </c>
       <c r="O76" s="16" t="n">
         <v>0</v>
@@ -6198,32 +6198,32 @@
     <row r="77">
       <c r="A77" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32967</t>
+          <t>PDMDEP-32984</t>
         </is>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
+          <t>[COMMUNE DE MONTELIMAR] - Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DU PONTET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier 2/2</t>
+          <t>Interface Civil net finance avec Littéralis</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="11" t="inlineStr">
@@ -6233,7 +6233,7 @@
       </c>
       <c r="H77" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="11" t="inlineStr">
@@ -6245,20 +6245,20 @@
         <v>6</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32974</t>
+          <t>PDMDEP-32990</t>
         </is>
       </c>
       <c r="M77" s="11" t="inlineStr">
         <is>
-          <t>00165260</t>
+          <t>00165270</t>
         </is>
       </c>
       <c r="N77" s="12" t="n">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="O77" s="16" t="n">
         <v>0</v>
@@ -6270,12 +6270,12 @@
     <row r="78">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32967</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[COMMUNE DU PONTET] - Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D78" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>COMMUNE DU PONTET</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Migration GeODP Placier 2/2</t>
         </is>
       </c>
       <c r="F78" s="14" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="H78" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="J78" s="14" t="n">
@@ -6321,16 +6321,16 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32974</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00165260</t>
         </is>
       </c>
       <c r="N78" s="15" t="n">
-        <v>680.8</v>
+        <v>200</v>
       </c>
       <c r="O78" s="16" t="n">
         <v>0</v>
@@ -6342,12 +6342,12 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
@@ -6357,12 +6357,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr">
@@ -6377,12 +6377,12 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J79" s="11" t="n">
@@ -6393,16 +6393,16 @@
       </c>
       <c r="L79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M79" s="11" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N79" s="12" t="n">
-        <v>2614.5</v>
+        <v>680.8</v>
       </c>
       <c r="O79" s="16" t="n">
         <v>0</v>
@@ -6414,32 +6414,32 @@
     <row r="80">
       <c r="A80" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F80" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="H80" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J80" s="14" t="n">
@@ -6465,16 +6465,16 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N80" s="15" t="n">
-        <v>403.074</v>
+        <v>2614.5</v>
       </c>
       <c r="O80" s="16" t="n">
         <v>0</v>
@@ -6486,32 +6486,32 @@
     <row r="81">
       <c r="A81" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="11" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
@@ -6537,19 +6537,19 @@
       </c>
       <c r="L81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M81" s="11" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O81" s="12" t="n">
-        <v>276</v>
+        <v>403.074</v>
+      </c>
+      <c r="O81" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P81" s="12" t="n">
         <v>0</v>
@@ -6558,32 +6558,32 @@
     <row r="82">
       <c r="A82" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F82" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -6593,12 +6593,12 @@
       </c>
       <c r="H82" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J82" s="14" t="n">
@@ -6609,19 +6609,19 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N82" s="15" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O82" s="16" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O82" s="15" t="n">
+        <v>276</v>
       </c>
       <c r="P82" s="15" t="n">
         <v>0</v>
@@ -6630,32 +6630,32 @@
     <row r="83">
       <c r="A83" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -6665,32 +6665,32 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J83" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K83" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M83" s="11" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N83" s="12" t="n">
-        <v>11278.05</v>
+        <v>142.1</v>
       </c>
       <c r="O83" s="16" t="n">
         <v>0</v>
@@ -6702,32 +6702,32 @@
     <row r="84">
       <c r="A84" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F84" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="H84" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J84" s="14" t="n">
@@ -6753,16 +6753,16 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N84" s="15" t="n">
-        <v>1000</v>
+        <v>11278.05</v>
       </c>
       <c r="O84" s="16" t="n">
         <v>0</v>
@@ -6774,32 +6774,32 @@
     <row r="85">
       <c r="A85" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32366</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>Commune de Pleneuf Val André</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>Migration de GEODP-Placier simple</t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I85" s="11" t="inlineStr">
@@ -6825,16 +6825,16 @@
       </c>
       <c r="L85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32372</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M85" s="11" t="inlineStr">
         <is>
-          <t>00161594</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N85" s="12" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="O85" s="16" t="n">
         <v>0</v>
@@ -6846,12 +6846,12 @@
     <row r="86">
       <c r="A86" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32366</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[Commune de Pleneuf Val André] - Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>Commune de Pleneuf Val André</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Migration de GEODP-Placier simple</t>
         </is>
       </c>
       <c r="F86" s="14" t="inlineStr">
@@ -6886,7 +6886,7 @@
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J86" s="14" t="n">
@@ -6897,16 +6897,16 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32372</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161594</t>
         </is>
       </c>
       <c r="N86" s="15" t="n">
-        <v>450</v>
+        <v>220</v>
       </c>
       <c r="O86" s="16" t="n">
         <v>0</v>
@@ -6918,32 +6918,32 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G87" s="11" t="inlineStr">
@@ -6953,32 +6953,32 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I87" s="11" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J87" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="L87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M87" s="11" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N87" s="12" t="n">
-        <v>910</v>
+        <v>450</v>
       </c>
       <c r="O87" s="16" t="n">
         <v>0</v>
@@ -6990,32 +6990,32 @@
     <row r="88">
       <c r="A88" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32193</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Estelle LEDUC</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTAUBAN</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>Migration GEODP2</t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F88" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -7025,32 +7025,32 @@
       </c>
       <c r="H88" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>19/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J88" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K88" s="14" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32202</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
         <is>
-          <t>00160782</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N88" s="15" t="n">
-        <v>3240</v>
+        <v>910</v>
       </c>
       <c r="O88" s="16" t="n">
         <v>0</v>
@@ -7062,27 +7062,27 @@
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32193</t>
         </is>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE MONTAUBAN] - Migration GEODP2</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Estelle LEDUC</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE MONTAUBAN</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Migration GEODP2</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="I89" s="11" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>19/03/2026</t>
         </is>
       </c>
       <c r="J89" s="11" t="n">
@@ -7113,16 +7113,16 @@
       </c>
       <c r="L89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32202</t>
         </is>
       </c>
       <c r="M89" s="11" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160782</t>
         </is>
       </c>
       <c r="N89" s="12" t="n">
-        <v>1050</v>
+        <v>3240</v>
       </c>
       <c r="O89" s="16" t="n">
         <v>0</v>
@@ -7134,27 +7134,27 @@
     <row r="90">
       <c r="A90" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F90" s="14" t="inlineStr">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J90" s="14" t="n">
@@ -7185,16 +7185,16 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N90" s="15" t="n">
-        <v>433.5</v>
+        <v>1050</v>
       </c>
       <c r="O90" s="16" t="n">
         <v>0</v>
@@ -7206,32 +7206,32 @@
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -7241,34 +7241,34 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J91" s="11" t="n">
         <v>7</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M91" s="11" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O91" s="12" t="n">
+        <v>433.5</v>
+      </c>
+      <c r="O91" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P91" s="12" t="n">
@@ -7278,32 +7278,32 @@
     <row r="92">
       <c r="A92" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F92" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -7313,34 +7313,34 @@
       </c>
       <c r="H92" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J92" s="14" t="n">
         <v>7</v>
       </c>
       <c r="K92" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N92" s="15" t="n">
-        <v>285</v>
-      </c>
-      <c r="O92" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P92" s="15" t="n">
@@ -7350,32 +7350,32 @@
     <row r="93">
       <c r="A93" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J93" s="11" t="n">
@@ -7401,16 +7401,16 @@
       </c>
       <c r="L93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M93" s="11" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N93" s="12" t="n">
-        <v>120</v>
+        <v>285</v>
       </c>
       <c r="O93" s="16" t="n">
         <v>0</v>
@@ -7422,32 +7422,32 @@
     <row r="94">
       <c r="A94" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F94" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H94" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J94" s="14" t="n">
@@ -7473,16 +7473,16 @@
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N94" s="15" t="n">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="O94" s="16" t="n">
         <v>0</v>
@@ -7494,27 +7494,27 @@
     <row r="95">
       <c r="A95" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -7529,32 +7529,32 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J95" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M95" s="11" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N95" s="12" t="n">
-        <v>203.5</v>
+        <v>210</v>
       </c>
       <c r="O95" s="16" t="n">
         <v>0</v>
@@ -7566,32 +7566,32 @@
     <row r="96">
       <c r="A96" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F96" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="H96" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I96" s="14" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J96" s="14" t="n">
@@ -7617,16 +7617,16 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31546</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
         <is>
-          <t>00157816</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N96" s="15" t="n">
-        <v>1088.5</v>
+        <v>203.5</v>
       </c>
       <c r="O96" s="16" t="n">
         <v>0</v>
@@ -7638,32 +7638,32 @@
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="11" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J97" s="11" t="n">
@@ -7689,16 +7689,16 @@
       </c>
       <c r="L97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M97" s="11" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N97" s="12" t="n">
-        <v>130</v>
+        <v>1088.5</v>
       </c>
       <c r="O97" s="16" t="n">
         <v>0</v>
@@ -7710,12 +7710,12 @@
     <row r="98">
       <c r="A98" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
       <c r="C98" s="14" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J98" s="14" t="n">
@@ -7761,16 +7761,16 @@
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31488</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157472</t>
         </is>
       </c>
       <c r="N98" s="15" t="n">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="O98" s="16" t="n">
         <v>0</v>
@@ -7782,12 +7782,12 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
@@ -7797,12 +7797,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J99" s="11" t="n">
@@ -7833,16 +7833,16 @@
       </c>
       <c r="L99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M99" s="11" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N99" s="12" t="n">
-        <v>130</v>
+        <v>210</v>
       </c>
       <c r="O99" s="16" t="n">
         <v>0</v>
@@ -7854,12 +7854,12 @@
     <row r="100">
       <c r="A100" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F100" s="14" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J100" s="14" t="n">
@@ -7905,16 +7905,16 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N100" s="15" t="n">
-        <v>255</v>
+        <v>130</v>
       </c>
       <c r="O100" s="16" t="n">
         <v>0</v>
@@ -7926,12 +7926,12 @@
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -7966,27 +7966,27 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J101" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K101" s="11" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M101" s="11" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N101" s="12" t="n">
-        <v>140</v>
+        <v>255</v>
       </c>
       <c r="O101" s="16" t="n">
         <v>0</v>
@@ -7998,32 +7998,32 @@
     <row r="102">
       <c r="A102" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F102" s="14" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G102" s="14" t="inlineStr">
@@ -8033,32 +8033,32 @@
       </c>
       <c r="H102" s="14" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J102" s="14" t="n">
         <v>9</v>
       </c>
       <c r="K102" s="14" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N102" s="15" t="n">
-        <v>230</v>
+        <v>140</v>
       </c>
       <c r="O102" s="16" t="n">
         <v>0</v>
@@ -8070,12 +8070,12 @@
     <row r="103">
       <c r="A103" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29964</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>SAINT DIZIER</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -8110,29 +8110,29 @@
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J103" s="11" t="n">
         <v>9</v>
       </c>
       <c r="K103" s="11" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29965</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M103" s="11" t="inlineStr">
         <is>
-          <t>00152739</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O103" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O103" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P103" s="12" t="n">
@@ -8142,27 +8142,27 @@
     <row r="104">
       <c r="A104" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29964</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t xml:space="preserve">[COMMUNE DE SAINT DIZIER] - Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>SAINT DIZIER</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t xml:space="preserve">Paramétrage et modélisation redevances occupation du domaine public sur Littéralis </t>
         </is>
       </c>
       <c r="F104" s="14" t="inlineStr">
@@ -8189,22 +8189,22 @@
         <v>9</v>
       </c>
       <c r="K104" s="14" t="n">
-        <v>3.5</v>
+        <v>0.5</v>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29965</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152739</t>
         </is>
       </c>
       <c r="N104" s="15" t="n">
-        <v>204.14</v>
-      </c>
-      <c r="O104" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O104" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P104" s="15" t="n">
@@ -8214,26 +8214,28 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-29012</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARCASSONNE</t>
-        </is>
-      </c>
-      <c r="E105" s="11" t="n">
-        <v/>
+          <t>MAIRE DE PONTARLIER</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
+        </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
         <is>
@@ -8252,29 +8254,29 @@
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>16/12/2025</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J105" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="L105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29014</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M105" s="11" t="inlineStr">
         <is>
-          <t>00147236</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O105" s="12" t="n">
+        <v>204.14</v>
+      </c>
+      <c r="O105" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P105" s="12" t="n">
@@ -8284,12 +8286,12 @@
     <row r="106">
       <c r="A106" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-29012</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>COMMUNE DE CARCASSONNE - LITTERALIS (Publi - Ixparapheur - DA/DPA)</t>
         </is>
       </c>
       <c r="C106" s="14" t="inlineStr">
@@ -8299,7 +8301,7 @@
       </c>
       <c r="D106" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
+          <t>COMMUNE DE CARCASSONNE</t>
         </is>
       </c>
       <c r="E106" s="14" t="n">
@@ -8317,34 +8319,34 @@
       </c>
       <c r="H106" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>16/12/2025</t>
         </is>
       </c>
       <c r="J106" s="14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K106" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-29014</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00147236</t>
         </is>
       </c>
       <c r="N106" s="15" t="n">
-        <v>401.54</v>
-      </c>
-      <c r="O106" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P106" s="15" t="n">
@@ -8354,12 +8356,12 @@
     <row r="107">
       <c r="A107" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
@@ -8369,13 +8371,11 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E107" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v/>
       </c>
       <c r="F107" s="11" t="inlineStr">
         <is>
@@ -8394,27 +8394,27 @@
       </c>
       <c r="I107" s="11" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J107" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K107" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M107" s="11" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N107" s="12" t="n">
-        <v>275</v>
+        <v>401.54</v>
       </c>
       <c r="O107" s="16" t="n">
         <v>0</v>
@@ -8477,18 +8477,18 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N108" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O108" s="15" t="n">
+        <v>275</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="15" t="n">
@@ -8549,18 +8549,18 @@
       </c>
       <c r="L109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M109" s="11" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N109" s="12" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O109" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="12" t="n">
@@ -8621,18 +8621,18 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N110" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="15" t="n">
+        <v>1790</v>
+      </c>
+      <c r="O110" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="15" t="n">
@@ -8693,12 +8693,12 @@
       </c>
       <c r="L111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M111" s="11" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N111" s="12" t="n">
@@ -8714,12 +8714,12 @@
     <row r="112">
       <c r="A112" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C112" s="14" t="inlineStr">
@@ -8729,11 +8729,13 @@
       </c>
       <c r="D112" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E112" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F112" s="14" t="inlineStr">
         <is>
@@ -8752,29 +8754,29 @@
       </c>
       <c r="I112" s="14" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J112" s="14" t="n">
         <v>11</v>
       </c>
       <c r="K112" s="14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27557</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>00144532</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N112" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O112" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O112" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P112" s="15" t="n">
@@ -8784,12 +8786,12 @@
     <row r="113">
       <c r="A113" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
@@ -8799,7 +8801,7 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -8817,32 +8819,32 @@
       </c>
       <c r="H113" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I113" s="11" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J113" s="11" t="n">
         <v>11</v>
       </c>
       <c r="K113" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M113" s="11" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N113" s="12" t="n">
-        <v>460</v>
+        <v>1000</v>
       </c>
       <c r="O113" s="16" t="n">
         <v>0</v>
@@ -8854,22 +8856,22 @@
     <row r="114">
       <c r="A114" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-24531</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>[CD 17] - Paramétrage de redevances 3J</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C114" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E114" s="14" t="n">
@@ -8892,44 +8894,44 @@
       </c>
       <c r="I114" s="14" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J114" s="14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K114" s="14" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27992</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>502114</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N114" s="15" t="n">
-        <v>3016.08</v>
+        <v>460</v>
       </c>
       <c r="O114" s="16" t="n">
-        <v>418.9</v>
+        <v>0</v>
       </c>
       <c r="P114" s="15" t="n">
-        <v>46.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24531</t>
         </is>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[CD 17] - Paramétrage de redevances 3J</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
@@ -8939,7 +8941,7 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -8962,54 +8964,54 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="J115" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K115" s="11" t="n">
-        <v>0.25</v>
+        <v>9</v>
       </c>
       <c r="L115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27992</t>
         </is>
       </c>
       <c r="M115" s="11" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>502114</t>
         </is>
       </c>
       <c r="N115" s="12" t="n">
-        <v>1200</v>
+        <v>3016.08</v>
       </c>
       <c r="O115" s="16" t="n">
-        <v>0</v>
+        <v>418.9</v>
       </c>
       <c r="P115" s="12" t="n">
-        <v>0</v>
+        <v>46.54</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C116" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E116" s="14" t="n">
@@ -9027,32 +9029,32 @@
       </c>
       <c r="H116" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J116" s="14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K116" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N116" s="15" t="n">
-        <v>3919.06</v>
+        <v>1200</v>
       </c>
       <c r="O116" s="16" t="n">
         <v>0</v>
@@ -9064,12 +9066,12 @@
     <row r="117">
       <c r="A117" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
@@ -9079,7 +9081,7 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -9102,29 +9104,29 @@
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J117" s="11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K117" s="11" t="n">
         <v>0.5</v>
       </c>
       <c r="L117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M117" s="11" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N117" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="12" t="n">
+        <v>3919.06</v>
+      </c>
+      <c r="O117" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="12" t="n">
@@ -9134,12 +9136,12 @@
     <row r="118">
       <c r="A118" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C118" s="14" t="inlineStr">
@@ -9149,7 +9151,7 @@
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E118" s="14" t="n">
@@ -9172,23 +9174,23 @@
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J118" s="14" t="n">
         <v>15</v>
       </c>
       <c r="K118" s="14" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N118" s="15" t="n">
@@ -9253,12 +9255,12 @@
       </c>
       <c r="L119" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M119" s="11" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N119" s="12" t="n">
@@ -9289,7 +9291,7 @@
       </c>
       <c r="D120" s="14" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E120" s="14" t="n">
@@ -9323,12 +9325,12 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N120" s="15" t="n">
@@ -9359,7 +9361,7 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -9393,12 +9395,12 @@
       </c>
       <c r="L121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M121" s="11" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N121" s="12" t="n">
@@ -9414,22 +9416,22 @@
     <row r="122">
       <c r="A122" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E122" s="14" t="n">
@@ -9452,23 +9454,23 @@
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J122" s="14" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K122" s="14" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N122" s="15" t="n">
@@ -9484,22 +9486,22 @@
     <row r="123">
       <c r="A123" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -9517,12 +9519,12 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J123" s="11" t="n">
@@ -9533,18 +9535,18 @@
       </c>
       <c r="L123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M123" s="11" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N123" s="12" t="n">
-        <v>250</v>
-      </c>
-      <c r="O123" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O123" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P123" s="12" t="n">
@@ -9554,22 +9556,22 @@
     <row r="124">
       <c r="A124" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E124" s="14" t="n">
@@ -9592,27 +9594,27 @@
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J124" s="14" t="n">
         <v>18</v>
       </c>
       <c r="K124" s="14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N124" s="15" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="O124" s="16" t="n">
         <v>0</v>
@@ -9624,12 +9626,12 @@
     <row r="125">
       <c r="A125" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
@@ -9639,7 +9641,7 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E125" s="11" t="n">
@@ -9657,34 +9659,34 @@
       </c>
       <c r="H125" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J125" s="11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K125" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M125" s="11" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N125" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O125" s="12" t="n">
+        <v>230</v>
+      </c>
+      <c r="O125" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="12" t="n">
@@ -9694,12 +9696,12 @@
     <row r="126">
       <c r="A126" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C126" s="14" t="inlineStr">
@@ -9709,7 +9711,7 @@
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E126" s="14" t="n">
@@ -9732,7 +9734,7 @@
       </c>
       <c r="I126" s="14" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J126" s="14" t="n">
@@ -9743,12 +9745,12 @@
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N126" s="15" t="n">
@@ -9764,12 +9766,12 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
@@ -9779,13 +9781,11 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E127" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v/>
       </c>
       <c r="F127" s="11" t="inlineStr">
         <is>
@@ -9794,27 +9794,35 @@
       </c>
       <c r="G127" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J127" s="11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K127" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L127" s="11" t="inlineStr"/>
-      <c r="M127" s="11" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L127" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N127" s="12" t="n">
         <v>0</v>
       </c>
@@ -9828,26 +9836,28 @@
     <row r="128">
       <c r="A128" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E128" s="14" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E128" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F128" s="14" t="inlineStr">
         <is>
@@ -9866,11 +9876,11 @@
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J128" s="14" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K128" s="14" t="n">
         <v>0.25</v>
@@ -9890,22 +9900,22 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -9923,7 +9933,7 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
@@ -9935,7 +9945,7 @@
         <v>22</v>
       </c>
       <c r="K129" s="11" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="L129" s="11" t="inlineStr"/>
       <c r="M129" s="11" t="inlineStr"/>
@@ -9952,22 +9962,22 @@
     <row r="130">
       <c r="A130" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E130" s="14" t="n">
@@ -9975,44 +9985,36 @@
       </c>
       <c r="F130" s="14" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H130" s="14" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J130" s="14" t="n">
         <v>22</v>
       </c>
       <c r="K130" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M130" s="14" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L130" s="14" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
       <c r="N130" s="15" t="n">
-        <v>240</v>
-      </c>
-      <c r="O130" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" s="15" t="n">
         <v>0</v>
       </c>
       <c r="P130" s="15" t="n">
@@ -10022,22 +10024,22 @@
     <row r="131">
       <c r="A131" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-18037</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>LE PERREUX SUR MARNE</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -10045,7 +10047,7 @@
       </c>
       <c r="F131" s="11" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G131" s="11" t="inlineStr">
@@ -10055,34 +10057,34 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I131" s="11" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J131" s="11" t="n">
         <v>22</v>
       </c>
       <c r="K131" s="11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28023</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M131" s="11" t="inlineStr">
         <is>
-          <t>454387</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N131" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O131" s="12" t="n">
+        <v>240</v>
+      </c>
+      <c r="O131" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="12" t="n">
@@ -10092,22 +10094,22 @@
     <row r="132">
       <c r="A132" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18037</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[LE PERREUX SUR MARNE] Modélisation/Paramétrage 2J civil net finances</t>
         </is>
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>LE PERREUX SUR MARNE</t>
         </is>
       </c>
       <c r="E132" s="14" t="n">
@@ -10120,7 +10122,7 @@
       </c>
       <c r="G132" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H132" s="14" t="inlineStr">
@@ -10130,17 +10132,25 @@
       </c>
       <c r="I132" s="14" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J132" s="14" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K132" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="L132" s="14" t="inlineStr"/>
-      <c r="M132" s="14" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L132" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-28023</t>
+        </is>
+      </c>
+      <c r="M132" s="14" t="inlineStr">
+        <is>
+          <t>454387</t>
+        </is>
+      </c>
       <c r="N132" s="15" t="n">
         <v>0</v>
       </c>
@@ -10154,22 +10164,22 @@
     <row r="133">
       <c r="A133" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E133" s="11" t="n">
@@ -10192,14 +10202,14 @@
       </c>
       <c r="I133" s="11" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J133" s="11" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K133" s="11" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L133" s="11" t="inlineStr"/>
       <c r="M133" s="11" t="inlineStr"/>
@@ -10216,12 +10226,12 @@
     <row r="134">
       <c r="A134" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-13280</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
         <is>
-          <t>[Arles] Littéralis Prime</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C134" s="14" t="inlineStr">
@@ -10231,7 +10241,7 @@
       </c>
       <c r="D134" s="14" t="inlineStr">
         <is>
-          <t>[Arles]</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E134" s="14" t="n">
@@ -10249,19 +10259,19 @@
       </c>
       <c r="H134" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="14" t="inlineStr">
         <is>
-          <t>10/11/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J134" s="14" t="n">
         <v>35</v>
       </c>
       <c r="K134" s="14" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="L134" s="14" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -10278,12 +10288,12 @@
     <row r="135">
       <c r="A135" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13280</t>
         </is>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Arles] Littéralis Prime</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
@@ -10293,7 +10303,7 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>[Arles]</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -10306,35 +10316,27 @@
       </c>
       <c r="G135" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H135" s="11" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I135" s="11" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>10/11/2023</t>
         </is>
       </c>
       <c r="J135" s="11" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K135" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L135" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M135" s="11" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L135" s="11" t="inlineStr"/>
+      <c r="M135" s="11" t="inlineStr"/>
       <c r="N135" s="12" t="n">
         <v>0</v>
       </c>
@@ -10348,22 +10350,22 @@
     <row r="136">
       <c r="A136" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C136" s="14" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D136" s="14" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E136" s="14" t="n">
@@ -10376,13 +10378,17 @@
       </c>
       <c r="G136" s="14" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H136" s="14" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H136" s="14" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I136" s="14" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J136" s="14" t="n">
@@ -10391,8 +10397,16 @@
       <c r="K136" s="14" t="n">
         <v>0.5</v>
       </c>
-      <c r="L136" s="14" t="inlineStr"/>
-      <c r="M136" s="14" t="inlineStr"/>
+      <c r="L136" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M136" s="14" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N136" s="15" t="n">
         <v>0</v>
       </c>
@@ -10406,12 +10420,12 @@
     <row r="137">
       <c r="A137" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
@@ -10421,7 +10435,7 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -10437,32 +10451,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H137" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H137" s="11" t="inlineStr"/>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J137" s="11" t="n">
         <v>37</v>
       </c>
       <c r="K137" s="11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="L137" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M137" s="11" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L137" s="11" t="inlineStr"/>
+      <c r="M137" s="11" t="inlineStr"/>
       <c r="N137" s="12" t="n">
         <v>0</v>
       </c>
@@ -10476,22 +10478,22 @@
     <row r="138">
       <c r="A138" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-12292</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
         <is>
-          <t>[CD06] Littéralis expert</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="14" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E138" s="14" t="n">
@@ -10504,29 +10506,33 @@
       </c>
       <c r="G138" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H138" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H138" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I138" s="14" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J138" s="14" t="n">
         <v>37</v>
       </c>
       <c r="K138" s="14" t="n">
-        <v>0.75</v>
+        <v>6.25</v>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-25456</t>
+          <t>PDMDEP-34532</t>
         </is>
       </c>
       <c r="M138" s="14" t="inlineStr">
         <is>
-          <t>424152</t>
+          <t>412263</t>
         </is>
       </c>
       <c r="N138" s="15" t="n">
@@ -10542,24 +10548,26 @@
     <row r="139">
       <c r="A139" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12292</t>
         </is>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C139" s="11" t="inlineStr"/>
+          <t>[CD06] Littéralis expert</t>
+        </is>
+      </c>
+      <c r="C139" s="11" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E139" s="11" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DES ALPES MARITIMES (CD06)</t>
+        </is>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v/>
       </c>
       <c r="F139" s="11" t="inlineStr">
         <is>
@@ -10568,17 +10576,13 @@
       </c>
       <c r="G139" s="11" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H139" s="11" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H139" s="11" t="inlineStr"/>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J139" s="11" t="n">
@@ -10587,8 +10591,16 @@
       <c r="K139" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="L139" s="11" t="inlineStr"/>
-      <c r="M139" s="11" t="inlineStr"/>
+      <c r="L139" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-25456</t>
+        </is>
+      </c>
+      <c r="M139" s="11" t="inlineStr">
+        <is>
+          <t>424152</t>
+        </is>
+      </c>
       <c r="N139" s="12" t="n">
         <v>0</v>
       </c>
@@ -10602,21 +10614,25 @@
     <row r="140">
       <c r="A140" s="13" t="inlineStr">
         <is>
-          <t>PSC-1363</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C140" s="14" t="inlineStr"/>
       <c r="D140" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE CADENET</t>
-        </is>
-      </c>
-      <c r="E140" s="14" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E140" s="14" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F140" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10624,20 +10640,24 @@
       </c>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H140" s="14" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H140" s="14" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I140" s="14" t="inlineStr">
         <is>
-          <t>02/10/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J140" s="14" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="K140" s="14" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L140" s="14" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -10654,18 +10674,18 @@
     <row r="141">
       <c r="A141" s="10" t="inlineStr">
         <is>
-          <t>PSC-1351</t>
+          <t>PSC-1363</t>
         </is>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr"/>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE VALENCAY</t>
+          <t>MAIRIE DE CADENET</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr"/>
@@ -10682,11 +10702,11 @@
       <c r="H141" s="11" t="inlineStr"/>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>23/09/2026</t>
+          <t>02/10/2026</t>
         </is>
       </c>
       <c r="J141" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K141" s="11" t="n">
         <v>0.25</v>
@@ -10706,18 +10726,18 @@
     <row r="142">
       <c r="A142" s="13" t="inlineStr">
         <is>
-          <t>PSC-1346</t>
+          <t>PSC-1351</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="C142" s="14" t="inlineStr"/>
       <c r="D142" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE BARRAUX</t>
+          <t>COMMUNE DE VALENCAY</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr"/>
@@ -10734,7 +10754,7 @@
       <c r="H142" s="14" t="inlineStr"/>
       <c r="I142" s="14" t="inlineStr">
         <is>
-          <t>22/09/2026</t>
+          <t>23/09/2026</t>
         </is>
       </c>
       <c r="J142" s="14" t="n">
@@ -10758,18 +10778,18 @@
     <row r="143">
       <c r="A143" s="10" t="inlineStr">
         <is>
-          <t>PSC-1339</t>
+          <t>PSC-1346</t>
         </is>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr"/>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>MAIRIE DE BALLAINVILLIERS</t>
+          <t>VILLE DE BARRAUX</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr"/>
@@ -10780,35 +10800,27 @@
       </c>
       <c r="G143" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr"/>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>22/09/2026</t>
         </is>
       </c>
       <c r="J143" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K143" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L143" s="11" t="inlineStr">
-        <is>
-          <t>PDMDEP-35312</t>
-        </is>
-      </c>
-      <c r="M143" s="11" t="inlineStr">
-        <is>
-          <t>00177354</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L143" s="11" t="inlineStr"/>
+      <c r="M143" s="11" t="inlineStr"/>
       <c r="N143" s="12" t="n">
-        <v>450</v>
-      </c>
-      <c r="O143" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" s="12" t="n">
         <v>0</v>
       </c>
       <c r="P143" s="12" t="n">
@@ -10818,18 +10830,18 @@
     <row r="144">
       <c r="A144" s="13" t="inlineStr">
         <is>
-          <t>PSC-1320</t>
+          <t>PSC-1339</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="C144" s="14" t="inlineStr"/>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>Commune de ETEL</t>
+          <t>MAIRIE DE BALLAINVILLIERS</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr"/>
@@ -10840,27 +10852,35 @@
       </c>
       <c r="G144" s="14" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H144" s="14" t="inlineStr"/>
       <c r="I144" s="14" t="inlineStr">
         <is>
-          <t>21/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J144" s="14" t="n">
         <v>3</v>
       </c>
       <c r="K144" s="14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L144" s="14" t="inlineStr"/>
-      <c r="M144" s="14" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L144" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-35312</t>
+        </is>
+      </c>
+      <c r="M144" s="14" t="inlineStr">
+        <is>
+          <t>00177354</t>
+        </is>
+      </c>
       <c r="N144" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O144" s="15" t="n">
+        <v>450</v>
+      </c>
+      <c r="O144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="15" t="n">
@@ -10870,18 +10890,18 @@
     <row r="145">
       <c r="A145" s="10" t="inlineStr">
         <is>
-          <t>PSC-1288</t>
+          <t>PSC-1320</t>
         </is>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr"/>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>Mairie d'Aubignan</t>
+          <t>Commune de ETEL</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr"/>
@@ -10898,14 +10918,14 @@
       <c r="H145" s="11" t="inlineStr"/>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="J145" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K145" s="11" t="n">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="L145" s="11" t="inlineStr"/>
       <c r="M145" s="11" t="inlineStr"/>
@@ -10922,18 +10942,18 @@
     <row r="146">
       <c r="A146" s="13" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1288</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="C146" s="14" t="inlineStr"/>
       <c r="D146" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>Mairie d'Aubignan</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr"/>
@@ -10944,31 +10964,23 @@
       </c>
       <c r="G146" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H146" s="14" t="inlineStr"/>
       <c r="I146" s="14" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="J146" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K146" s="14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L146" s="14" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M146" s="14" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="L146" s="14" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
       <c r="N146" s="15" t="n">
         <v>0</v>
       </c>
@@ -10982,18 +10994,18 @@
     <row r="147">
       <c r="A147" s="10" t="inlineStr">
         <is>
-          <t>PSC-1047</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr"/>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr"/>
@@ -11010,61 +11022,121 @@
       <c r="H147" s="11" t="inlineStr"/>
       <c r="I147" s="11" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J147" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K147" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L147" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M147" s="11" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="inlineStr">
+        <is>
+          <t>PSC-1047</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr"/>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>Mairie de Plan d'Orgon  - LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr"/>
+      <c r="F148" s="14" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H148" s="14" t="inlineStr"/>
+      <c r="I148" s="14" t="inlineStr">
+        <is>
           <t>04/11/2025</t>
         </is>
       </c>
-      <c r="J147" s="11" t="n">
+      <c r="J148" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="K147" s="11" t="n">
+      <c r="K148" s="14" t="n">
         <v>0.25</v>
       </c>
-      <c r="L147" s="11" t="inlineStr">
+      <c r="L148" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-26768</t>
         </is>
       </c>
-      <c r="M147" s="11" t="inlineStr">
+      <c r="M148" s="14" t="inlineStr">
         <is>
           <t>00141775</t>
         </is>
       </c>
-      <c r="N147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O147" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P147" s="12" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="17" t="inlineStr">
+      <c r="N148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O148" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" s="15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B148" s="17" t="inlineStr"/>
-      <c r="C148" s="17" t="inlineStr"/>
-      <c r="D148" s="17" t="inlineStr"/>
-      <c r="E148" s="17" t="inlineStr"/>
-      <c r="F148" s="17" t="inlineStr"/>
-      <c r="G148" s="17" t="inlineStr"/>
-      <c r="H148" s="17" t="inlineStr"/>
-      <c r="I148" s="17" t="inlineStr"/>
-      <c r="J148" s="17" t="inlineStr"/>
-      <c r="K148" s="17" t="inlineStr"/>
-      <c r="L148" s="17" t="inlineStr"/>
-      <c r="M148" s="17" t="inlineStr"/>
-      <c r="N148" s="18" t="n">
+      <c r="B149" s="17" t="inlineStr"/>
+      <c r="C149" s="17" t="inlineStr"/>
+      <c r="D149" s="17" t="inlineStr"/>
+      <c r="E149" s="17" t="inlineStr"/>
+      <c r="F149" s="17" t="inlineStr"/>
+      <c r="G149" s="17" t="inlineStr"/>
+      <c r="H149" s="17" t="inlineStr"/>
+      <c r="I149" s="17" t="inlineStr"/>
+      <c r="J149" s="17" t="inlineStr"/>
+      <c r="K149" s="17" t="inlineStr"/>
+      <c r="L149" s="17" t="inlineStr"/>
+      <c r="M149" s="17" t="inlineStr"/>
+      <c r="N149" s="18" t="n">
         <v>120486.717</v>
       </c>
-      <c r="O148" s="18" t="n">
+      <c r="O149" s="18" t="n">
         <v>5322.2</v>
       </c>
-      <c r="P148" s="18" t="n">
-        <v>43.6</v>
+      <c r="P149" s="18" t="n">
+        <v>42.72</v>
       </c>
     </row>
   </sheetData>
@@ -11213,6 +11285,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A148" r:id="rId144"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11224,13 +11297,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -11250,7 +11323,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 5 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 7 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -11315,22 +11388,22 @@
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34287</t>
+          <t>PDMDEP-35469</t>
         </is>
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
+          <t>[COMMUNE DE VENCE] -  Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE LUNEL</t>
+          <t>COMMUNE DE VENCE</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP </t>
+          <t xml:space="preserve"> Migration GeODP Placier Terrasse</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
@@ -11340,7 +11413,7 @@
       </c>
       <c r="F5" s="11" t="inlineStr">
         <is>
-          <t>Prestation offerte</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="G5" s="11" t="inlineStr">
@@ -11353,37 +11426,37 @@
       </c>
       <c r="I5" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34294</t>
+          <t>PDMDEP-35476</t>
         </is>
       </c>
       <c r="J5" s="11" t="inlineStr">
         <is>
-          <t>00171435</t>
+          <t>00180644</t>
         </is>
       </c>
       <c r="K5" s="12" t="n">
-        <v>1630</v>
+        <v>815</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-34249</t>
+          <t>PDMDEP-35227</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
+          <t xml:space="preserve">[VILLE DE CHAUNY] - Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIENNE</t>
+          <t>VILLE DE CHAUNY</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration Placier et ODP </t>
+          <t xml:space="preserve">Migration de GEODP-Placier + Remise en service paiement cb + Pax + Formation </t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -11393,7 +11466,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -11406,12 +11479,12 @@
       </c>
       <c r="I6" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34256</t>
+          <t>PDMDEP-35234</t>
         </is>
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>00171362</t>
+          <t>00179117</t>
         </is>
       </c>
       <c r="K6" s="15" t="n">
@@ -11421,22 +11494,22 @@
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t>PDMDEP-34012</t>
+          <t>PDMDEP-34287</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LUNEL] - Migration GeODP </t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>COMMUNE DE LUNEL</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Migration module Placier</t>
+          <t xml:space="preserve">Migration GeODP </t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -11446,7 +11519,7 @@
       </c>
       <c r="F7" s="11" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="G7" s="11" t="inlineStr">
@@ -11459,12 +11532,12 @@
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34019</t>
+          <t>PDMDEP-34294</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>00170492</t>
+          <t>00171435</t>
         </is>
       </c>
       <c r="K7" s="12" t="n">
@@ -11474,22 +11547,22 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-34249</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t xml:space="preserve">[COMMUNE DE VIENNE] - Migration Placier et ODP </t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>COMMUNE DE VIENNE</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t xml:space="preserve">Migration Placier et ODP </t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -11512,12 +11585,12 @@
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31819</t>
+          <t>PDMDEP-34256</t>
         </is>
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>00159472</t>
+          <t>00171362</t>
         </is>
       </c>
       <c r="K8" s="15" t="n">
@@ -11527,73 +11600,179 @@
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
         <is>
+          <t>PDMDEP-34012</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>[COMMUNE DE BIARRITZ] - Migration module Placier</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>COMMUNE DE BIARRITZ</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Migration module Placier</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34019</t>
+        </is>
+      </c>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>00170492</t>
+        </is>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>PDMDEP-31812</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>COMMUNE PROVINS</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Migration V2 classique</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>PDMDEP-31819</t>
+        </is>
+      </c>
+      <c r="J10" s="14" t="inlineStr">
+        <is>
+          <t>00159472</t>
+        </is>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
           <t>PDMDEP-31479</t>
         </is>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 </t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C11" s="11" t="inlineStr">
         <is>
           <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Migration vers GeoDP V2</t>
         </is>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E11" s="11" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F9" s="11" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G11" s="11" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="H11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="11" t="inlineStr">
         <is>
           <t>PDMDEP-31486</t>
         </is>
       </c>
-      <c r="J9" s="11" t="inlineStr">
+      <c r="J11" s="11" t="inlineStr">
         <is>
           <t>00157474</t>
         </is>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>815</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr"/>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="17" t="inlineStr"/>
-      <c r="J10" s="17" t="inlineStr"/>
-      <c r="K10" s="18" t="n">
-        <v>5705</v>
+      <c r="B12" s="17" t="inlineStr"/>
+      <c r="C12" s="17" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr"/>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="17" t="inlineStr"/>
+      <c r="H12" s="17" t="inlineStr"/>
+      <c r="I12" s="17" t="inlineStr"/>
+      <c r="J12" s="17" t="inlineStr"/>
+      <c r="K12" s="18" t="n">
+        <v>7335</v>
       </c>
     </row>
   </sheetData>
@@ -11604,6 +11783,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12078,16 +12259,16 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>77</v>
+        <v>79.25</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>13.25</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>4.83</v>
+        <v>5.08</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>95.08</v>
+        <v>97.58</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>8.25</v>
@@ -12097,7 +12278,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>19.2%</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12320,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>45.58</v>
+        <v>46.08</v>
       </c>
     </row>
   </sheetData>
@@ -12227,16 +12408,16 @@
         <v>508290</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>220394</v>
+        <v>225294</v>
       </c>
       <c r="D5" s="24" t="n">
-        <v>287896</v>
+        <v>282996</v>
       </c>
       <c r="E5" s="24" t="n">
         <v>220984</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>21551</v>
+        <v>16651</v>
       </c>
       <c r="G5" s="24" t="n">
         <v>18055</v>
@@ -12277,16 +12458,16 @@
         <v>244977</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>151333</v>
+        <v>156233</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>93644</v>
+        <v>88744</v>
       </c>
       <c r="E7" s="26" t="n">
         <v>46056</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>12376</v>
+        <v>7476</v>
       </c>
       <c r="G7" s="26" t="n">
         <v>10431</v>
